--- a/reports/Washroom_Summary_Details_2026.xlsx
+++ b/reports/Washroom_Summary_Details_2026.xlsx
@@ -23,7 +23,38 @@
     <sheet name="Baby Room Details" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="Washroom Assets Summery" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Mall Washroom Deatils'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Mall Washroom Deatils'!$A$1:$I$65</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Staff Washroom Deatils'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Staff Washroom Deatils'!$A$1:$J$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'External Staff Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'External Staff Washroom'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'FAE Washroom Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'FAE Washroom Details'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'FAE Handicap Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'FAE Handicap Washroom'!$A$1:$G$23</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'FAE Staff Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'FAE Staff Washroom'!$A$1:$I$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Mall Handicap Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Mall Handicap Washroom'!$A$1:$G$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Zabeel Washroom Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Zabeel Washroom Details'!$A$1:$J$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Zabeel Handicap Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Zabeel Handicap Washroom'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'CT Washroom Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="9">'CT Washroom Details'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'CT Handicap Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'CT Handicap Washroom'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'FV Washroom Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'FV Washroom Details'!$A$1:$I$27</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'FV Handicap Washroom'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'FV Handicap Washroom'!$A$1:$H$25</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Baby Room Details'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'Baby Room Details'!$A$1:$G$78</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'Washroom Assets Summery'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'Washroom Assets Summery'!$A$1:$H$15</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -615,7 +646,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2452,6 +2483,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2459,7 +2491,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2820,6 +2852,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2827,7 +2860,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3089,6 +3122,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3096,7 +3130,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -3925,6 +3959,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3932,7 +3967,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -4626,6 +4661,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4633,7 +4669,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6472,6 +6508,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6479,7 +6516,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -6896,6 +6933,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -6903,7 +6941,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -7442,6 +7480,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7449,7 +7488,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8199,6 +8238,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -8206,7 +8246,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -8846,6 +8886,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -8854,7 +8895,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9421,6 +9462,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -9428,7 +9470,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -9965,6 +10007,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -9972,7 +10015,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -10290,6 +10333,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -10297,7 +10341,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -10858,6 +10902,7 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -10865,7 +10910,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -11206,5 +11251,6 @@
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>